--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1689,6 +1689,127 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>108161038</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>662869</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6634350</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 ex. i barrmatta och gles mossvegetation, under gran, på blockrikt, litet höjdparti. Trädskikt består huvudsakligen av gran, men enstaka klen björk i närheten samt en lindgrupp.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Ca. 40-årig granplantering, på blockrikt, litet höjdparti.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1679,6 +1679,122 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122492111</v>
+      </c>
+      <c r="B10" t="n">
+        <v>83261</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>662869</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6634351</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Återfynd på lokalen upptäckt av Aronsson &amp; Björkén 2023.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83261</v>
+        <v>83262</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1698,11 +1698,6 @@
       </c>
       <c r="E10" t="n">
         <v>1445</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Bombmurkla</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83262</v>
+        <v>83266</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1698,6 +1698,11 @@
       </c>
       <c r="E10" t="n">
         <v>1445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83266</v>
+        <v>83267</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83267</v>
+        <v>83270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83372</v>
+        <v>83376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1724,6 +1724,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norredatorp, Upl</t>
@@ -1779,8 +1781,14 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Ung granskog (ca 40 år).</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1793,7 +1801,11 @@
           <t>Viktor Lund, Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83376</v>
+        <v>83379</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83379</v>
+        <v>83381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83381</v>
+        <v>83383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83383</v>
+        <v>83386</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1684,7 +1684,7 @@
         <v>122492111</v>
       </c>
       <c r="B10" t="n">
-        <v>83386</v>
+        <v>83395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1806,6 +1806,486 @@
           <t>Uppföljning bombmurkla 2025</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123763916</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83395</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>662867</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6634350</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123763945</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105415</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>662934</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6634368</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123763818</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56830</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>662750</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6634176</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123763831</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56939</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>662841</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6634280</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763916</v>
+        <v>123763818</v>
       </c>
       <c r="B11" t="n">
-        <v>83395</v>
+        <v>56833</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,52 +1821,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1445</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662867</v>
+        <v>662750</v>
       </c>
       <c r="R11" t="n">
-        <v>6634350</v>
+        <v>6634176</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,18 +1903,12 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1931,7 +1930,7 @@
         <v>123763945</v>
       </c>
       <c r="B12" t="n">
-        <v>105415</v>
+        <v>105430</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2039,10 +2038,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763818</v>
+        <v>123763831</v>
       </c>
       <c r="B13" t="n">
-        <v>56830</v>
+        <v>56942</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2055,16 +2054,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100065</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2083,7 +2082,11 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2095,10 +2098,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662750</v>
+        <v>662841</v>
       </c>
       <c r="R13" t="n">
-        <v>6634176</v>
+        <v>6634280</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2128,9 +2131,19 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,10 +2170,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763831</v>
+        <v>123763916</v>
       </c>
       <c r="B14" t="n">
-        <v>56939</v>
+        <v>83400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,61 +2182,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>1445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662841</v>
+        <v>662867</v>
       </c>
       <c r="R14" t="n">
-        <v>6634280</v>
+        <v>6634350</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2250,19 +2254,14 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2271,6 +2270,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763818</v>
+        <v>123763831</v>
       </c>
       <c r="B11" t="n">
-        <v>56833</v>
+        <v>56943</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1825,16 +1825,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100065</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1853,7 +1853,11 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1865,10 +1869,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662750</v>
+        <v>662841</v>
       </c>
       <c r="R11" t="n">
-        <v>6634176</v>
+        <v>6634280</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1898,9 +1902,19 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,10 +1941,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763945</v>
+        <v>123763818</v>
       </c>
       <c r="B12" t="n">
-        <v>105430</v>
+        <v>56834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1943,45 +1957,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>100065</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662934</v>
+        <v>662750</v>
       </c>
       <c r="R12" t="n">
-        <v>6634368</v>
+        <v>6634176</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2019,7 +2041,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2038,10 +2059,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763831</v>
+        <v>123763945</v>
       </c>
       <c r="B13" t="n">
-        <v>56942</v>
+        <v>105432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2054,57 +2075,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662841</v>
+        <v>662934</v>
       </c>
       <c r="R13" t="n">
-        <v>6634280</v>
+        <v>6634368</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2131,27 +2140,18 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>123763916</v>
       </c>
       <c r="B14" t="n">
-        <v>83400</v>
+        <v>83402</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763831</v>
+        <v>123763916</v>
       </c>
       <c r="B11" t="n">
-        <v>56943</v>
+        <v>83402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,61 +1821,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>1445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662841</v>
+        <v>662867</v>
       </c>
       <c r="R11" t="n">
-        <v>6634280</v>
+        <v>6634350</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1902,19 +1893,14 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1923,6 +1909,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2062,7 +2049,7 @@
         <v>123763945</v>
       </c>
       <c r="B13" t="n">
-        <v>105432</v>
+        <v>105007</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2170,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763916</v>
+        <v>123763831</v>
       </c>
       <c r="B14" t="n">
-        <v>83402</v>
+        <v>56943</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2182,52 +2169,61 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1445</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662867</v>
+        <v>662841</v>
       </c>
       <c r="R14" t="n">
-        <v>6634350</v>
+        <v>6634280</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2254,14 +2250,19 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2270,7 +2271,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763916</v>
+        <v>123763818</v>
       </c>
       <c r="B11" t="n">
-        <v>83402</v>
+        <v>56834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,52 +1821,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1445</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662867</v>
+        <v>662750</v>
       </c>
       <c r="R11" t="n">
-        <v>6634350</v>
+        <v>6634176</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,18 +1903,12 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,10 +1927,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763818</v>
+        <v>123763916</v>
       </c>
       <c r="B12" t="n">
-        <v>56834</v>
+        <v>83402</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1940,57 +1939,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100065</v>
+        <v>1445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662750</v>
+        <v>662867</v>
       </c>
       <c r="R12" t="n">
-        <v>6634176</v>
+        <v>6634350</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2022,12 +2016,18 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763945</v>
+        <v>123763831</v>
       </c>
       <c r="B13" t="n">
-        <v>105007</v>
+        <v>56943</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2062,45 +2062,57 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221141</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662934</v>
+        <v>662841</v>
       </c>
       <c r="R13" t="n">
-        <v>6634368</v>
+        <v>6634280</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2127,18 +2139,27 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2157,10 +2178,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763831</v>
+        <v>123763945</v>
       </c>
       <c r="B14" t="n">
-        <v>56943</v>
+        <v>105007</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,57 +2194,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>221141</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662841</v>
+        <v>662934</v>
       </c>
       <c r="R14" t="n">
-        <v>6634280</v>
+        <v>6634368</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2250,27 +2259,18 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763818</v>
+        <v>123763945</v>
       </c>
       <c r="B11" t="n">
-        <v>56834</v>
+        <v>105007</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1825,53 +1825,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100065</v>
+        <v>221141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662750</v>
+        <v>662934</v>
       </c>
       <c r="R11" t="n">
-        <v>6634176</v>
+        <v>6634368</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1909,6 +1901,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2046,10 +2039,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763831</v>
+        <v>123763818</v>
       </c>
       <c r="B13" t="n">
-        <v>56943</v>
+        <v>56834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2062,16 +2055,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>100065</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2090,11 +2083,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2106,10 +2095,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662841</v>
+        <v>662750</v>
       </c>
       <c r="R13" t="n">
-        <v>6634280</v>
+        <v>6634176</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2139,19 +2128,9 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>18:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2178,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763945</v>
+        <v>123763831</v>
       </c>
       <c r="B14" t="n">
-        <v>105007</v>
+        <v>56943</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2194,45 +2173,57 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662934</v>
+        <v>662841</v>
       </c>
       <c r="R14" t="n">
-        <v>6634368</v>
+        <v>6634280</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2259,18 +2250,27 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763945</v>
+        <v>123763916</v>
       </c>
       <c r="B11" t="n">
-        <v>105007</v>
+        <v>83402</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,35 +1821,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221141</v>
+        <v>1445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1857,13 +1860,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662934</v>
+        <v>662867</v>
       </c>
       <c r="R11" t="n">
-        <v>6634368</v>
+        <v>6634350</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1893,6 +1896,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,10 +1928,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763916</v>
+        <v>123763831</v>
       </c>
       <c r="B12" t="n">
-        <v>83402</v>
+        <v>56943</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1932,52 +1940,61 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1445</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662867</v>
+        <v>662841</v>
       </c>
       <c r="R12" t="n">
-        <v>6634350</v>
+        <v>6634280</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2004,14 +2021,19 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,7 +2042,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2039,10 +2060,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763818</v>
+        <v>123763945</v>
       </c>
       <c r="B13" t="n">
-        <v>56834</v>
+        <v>105007</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2055,53 +2076,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100065</v>
+        <v>221141</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662750</v>
+        <v>662934</v>
       </c>
       <c r="R13" t="n">
-        <v>6634176</v>
+        <v>6634368</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2139,6 +2152,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2157,10 +2171,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763831</v>
+        <v>123763818</v>
       </c>
       <c r="B14" t="n">
-        <v>56943</v>
+        <v>56834</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2173,16 +2187,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>100065</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2201,11 +2215,7 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2217,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662841</v>
+        <v>662750</v>
       </c>
       <c r="R14" t="n">
-        <v>6634280</v>
+        <v>6634176</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2250,19 +2260,9 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763916</v>
+        <v>123763818</v>
       </c>
       <c r="B11" t="n">
-        <v>83402</v>
+        <v>56834</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,52 +1821,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1445</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662867</v>
+        <v>662750</v>
       </c>
       <c r="R11" t="n">
-        <v>6634350</v>
+        <v>6634176</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1898,18 +1903,12 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,10 +1927,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763831</v>
+        <v>123763916</v>
       </c>
       <c r="B12" t="n">
-        <v>56943</v>
+        <v>83402</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1940,61 +1939,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>1445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662841</v>
+        <v>662867</v>
       </c>
       <c r="R12" t="n">
-        <v>6634280</v>
+        <v>6634350</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2021,19 +2011,14 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2042,6 +2027,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2171,10 +2157,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763818</v>
+        <v>123763831</v>
       </c>
       <c r="B14" t="n">
-        <v>56834</v>
+        <v>56943</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,16 +2173,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100065</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2215,7 +2201,11 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2227,10 +2217,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662750</v>
+        <v>662841</v>
       </c>
       <c r="R14" t="n">
-        <v>6634176</v>
+        <v>6634280</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2260,9 +2250,19 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1809,10 +1809,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763916</v>
+        <v>123763831</v>
       </c>
       <c r="B11" t="n">
-        <v>83424</v>
+        <v>56965</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1821,52 +1821,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1445</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662867</v>
+        <v>662841</v>
       </c>
       <c r="R11" t="n">
-        <v>6634350</v>
+        <v>6634280</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1893,14 +1902,19 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1909,7 +1923,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1928,10 +1941,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763831</v>
+        <v>123763945</v>
       </c>
       <c r="B12" t="n">
-        <v>56965</v>
+        <v>105029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1944,57 +1957,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>221141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662841</v>
+        <v>662934</v>
       </c>
       <c r="R12" t="n">
-        <v>6634280</v>
+        <v>6634368</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2021,27 +2022,18 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2060,10 +2052,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763818</v>
+        <v>123763916</v>
       </c>
       <c r="B13" t="n">
-        <v>56856</v>
+        <v>83424</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2072,57 +2064,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100065</v>
+        <v>1445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662750</v>
+        <v>662867</v>
       </c>
       <c r="R13" t="n">
-        <v>6634176</v>
+        <v>6634350</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2154,12 +2141,18 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2178,10 +2171,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763945</v>
+        <v>123763818</v>
       </c>
       <c r="B14" t="n">
-        <v>105029</v>
+        <v>56856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2194,45 +2187,53 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221141</v>
+        <v>100065</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Norreda torp, V, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662934</v>
+        <v>662750</v>
       </c>
       <c r="R14" t="n">
-        <v>6634368</v>
+        <v>6634176</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2270,7 +2271,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662746.5089489664</v>
+        <v>662747</v>
       </c>
       <c r="R2" t="n">
-        <v>6634236.851183858</v>
+        <v>6634237</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>65874240</v>
       </c>
       <c r="B3" t="n">
-        <v>95737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662746.5089489664</v>
+        <v>662747</v>
       </c>
       <c r="R3" t="n">
-        <v>6634236.851183858</v>
+        <v>6634237</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -869,19 +849,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>65874240</v>
       </c>
       <c r="B3" t="n">
-        <v>98130</v>
+        <v>98131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>106245</v>
+        <v>106246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>65874240</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>106246</v>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>65874240</v>
       </c>
       <c r="B3" t="n">
-        <v>98132</v>
+        <v>98135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>106245</v>
+        <v>106251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>65874240</v>
       </c>
       <c r="B3" t="n">
-        <v>98135</v>
+        <v>98141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>106251</v>
+        <v>106255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>65874240</v>
       </c>
       <c r="B3" t="n">
-        <v>98141</v>
+        <v>98144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65879747</v>
       </c>
       <c r="B2" t="n">
-        <v>106255</v>
+        <v>106260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>65874240</v>
       </c>
       <c r="B3" t="n">
-        <v>98144</v>
+        <v>98149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1372,12 +1372,7 @@
         <v>111611137</v>
       </c>
       <c r="B8" t="n">
-        <v>89416</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,16 +1407,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662817.7710425339</v>
+        <v>662817</v>
       </c>
       <c r="R8" t="n">
-        <v>6634245.514864446</v>
+        <v>6634246</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1451,24 +1448,14 @@
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 ex., 0,2-4 m upp, i gamla övervallade stamsår på levande asp, omkr. 177 cm.</t>
+          <t>5 ex., 0,2-4 m upp på levande asp, omkr. 177 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,6 +1464,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1492,7 +1480,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Gamla övervallade stamsår på levande asp, omkr. 177 cm. # Asp</t>
+          <t>Stammen av levande asp, omkr. 177 cm. # Asp</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>111611137</v>
       </c>
       <c r="B8" t="n">
-        <v>91903</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>111611137</v>
       </c>
       <c r="B8" t="n">
-        <v>91909</v>
+        <v>91919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -1372,7 +1372,7 @@
         <v>111611137</v>
       </c>
       <c r="B8" t="n">
-        <v>91919</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65879747</v>
+        <v>111611166</v>
       </c>
       <c r="B2" t="n">
-        <v>106263</v>
+        <v>89799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>37</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Jättekamskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Amanita ceciliae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Berk. &amp; Broome) Bas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>200 m V om Norredatorp, Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662747</v>
+        <v>663058</v>
       </c>
       <c r="R2" t="n">
-        <v>6634237</v>
+        <v>6634513</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-12-31</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>1 ex. under hassel, intill levande jätteek, omkr. 515 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,68 +770,70 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Löv-/blandskog med ek, asp, björk, lind, gran och hassel.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Thulin</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65874240</v>
+        <v>111424406</v>
       </c>
       <c r="B3" t="n">
-        <v>98151</v>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>569</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>200 m V om Norredatorp, Upl</t>
+          <t>Norrsjön, Norrsjön, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662747</v>
+        <v>662973</v>
       </c>
       <c r="R3" t="n">
-        <v>6634237</v>
+        <v>6634316</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1999-01-01</t>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,31 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Thulin</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75624376</v>
+        <v>111611161</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +910,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662974.7009473066</v>
+        <v>662880</v>
       </c>
       <c r="R4" t="n">
-        <v>6634394.428135857</v>
+        <v>6634380</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,27 +973,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2005-04-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2005-04-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död, kvarsittande gren på levande gran, omkr. 129 cm.</t>
+          <t>1 ex. på nedfallen murken gren från levande asp, i granplantering med inslag av lövträd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,14 +995,19 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ca. 40-årig granplantering med inslag av lövträd.</t>
+        </is>
+      </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Asp</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Död, kvarsittande gren på levande gran. # Gran</t>
+          <t>Nedfallen murken gren från levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1014,56 +1025,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75954920</v>
+        <v>75739869</v>
       </c>
       <c r="B5" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79795</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>374</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norreda torp, Upl</t>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662822.3657914202</v>
+        <v>663055</v>
       </c>
       <c r="R5" t="n">
-        <v>6634255.789517657</v>
+        <v>6634508</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,27 +1090,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2004-06-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-04-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2004-06-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2005-04-08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>i naturskog</t>
+          <t>På stammen av levande ek, omkr. 506 cm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,73 +1109,76 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Pär Eriksson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pär Eriksson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107764941</v>
+        <v>65874240</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norredatorp, Upl</t>
+          <t>200 m V om Norredatorp, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662970.0223840788</v>
+        <v>662747</v>
       </c>
       <c r="R6" t="n">
-        <v>6634374.580668435</v>
+        <v>6634237</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,22 +1202,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-04-02</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-04-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>1999-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,71 +1227,63 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Mats Thulin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108161038</v>
+        <v>16830581</v>
       </c>
       <c r="B7" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1445</v>
+        <v>655</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+          <t>Lagga kyrka, 4,3 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>662869</v>
+        <v>663053</v>
       </c>
       <c r="R7" t="n">
-        <v>6634350</v>
+        <v>6634515</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,17 +1310,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-04-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 ex. i barrmatta och gles mossvegetation, under gran, på blockrikt, litet höjdparti. Trädskikt består huvudsakligen av gran, men enstaka klen björk i närheten samt en lindgrupp.</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,33 +1324,53 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Ca. 40-årig granplantering, på blockrikt, litet höjdparti.</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Levande träd med grov stam</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Quercus robur # Levande träd med grov stam</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111611137</v>
+        <v>385227</v>
       </c>
       <c r="B8" t="n">
-        <v>91929</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,28 +1395,17 @@
           <t>Niemelä</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+          <t>350 M V NORREDATORP (11I6d03), Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>662817</v>
+        <v>662606</v>
       </c>
       <c r="R8" t="n">
-        <v>6634246</v>
+        <v>6634281</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1445,17 +1432,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>1998-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>1998-06-30</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 ex., 0,2-4 m upp på levande asp, omkr. 177 cm.</t>
+          <t>110863031 / PHE POPU / Enstaka-sparsam (1)  / OBJ.AREA:0,1 ha</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,93 +1451,69 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Ca. 40-årig granplantering med inslag av lövträd.</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stammen av levande asp, omkr. 177 cm. # Asp</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Roine Schenning</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111611161</v>
+        <v>7105650</v>
       </c>
       <c r="B9" t="n">
-        <v>90151</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>366</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+          <t>Lagga kyrka, 4,0 km NO-ut, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>662879.9742724057</v>
+        <v>662771</v>
       </c>
       <c r="R9" t="n">
-        <v>6634380.199484827</v>
+        <v>6634295</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,27 +1540,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-09-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 ex. på nedfallen murken gren från levande asp, i granplantering med inslag av lövträd.</t>
+          <t>Aspstammens omkrets= 156 cm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,72 +1562,76 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Ca. 40-årig granplantering med inslag av lövträd.</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Asp</t>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Nedfallen murken gren från levande asp. # Asp</t>
+          <t>Stem on living tree # Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122492111</v>
+        <v>62588870</v>
       </c>
       <c r="B10" t="n">
-        <v>83395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1445</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1682,21 +1639,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norredatorp, Upl</t>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>662869</v>
+        <v>662849</v>
       </c>
       <c r="R10" t="n">
-        <v>6634351</v>
+        <v>6634191</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1720,17 +1675,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2006-02-21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Återfynd på lokalen upptäckt av Aronsson &amp; Björkén 2023.</t>
+          <t>2 ex. på levande asp, omkr. 105 cm.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,43 +1694,38 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Ung granskog (ca 40 år).</t>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Levande asp. # Asp</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763831</v>
+        <v>75954920</v>
       </c>
       <c r="B11" t="n">
-        <v>56965</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,54 +1733,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norreda torp, V, Upl</t>
+          <t>Norreda torp, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>662841</v>
+        <v>662822</v>
       </c>
       <c r="R11" t="n">
-        <v>6634280</v>
+        <v>6634256</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1857,22 +1790,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2004-06-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2004-06-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>i naturskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,33 +1809,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Pär Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763945</v>
+        <v>111611137</v>
       </c>
       <c r="B12" t="n">
-        <v>105029</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,45 +1839,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221141</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norreda torp, V, Upl</t>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>662934</v>
+        <v>662817</v>
       </c>
       <c r="R12" t="n">
-        <v>6634368</v>
+        <v>6634246</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1977,12 +1904,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 ex., 0,2-4 m upp på levande asp, omkr. 177 cm.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1995,79 +1927,79 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Ca. 40-årig granplantering med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp, omkr. 177 cm. # Asp</t>
+        </is>
+      </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763916</v>
+        <v>107764023</v>
       </c>
       <c r="B13" t="n">
-        <v>83424</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norreda torp, V, Upl</t>
+          <t>Norrsjön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>662867</v>
+        <v>663027</v>
       </c>
       <c r="R13" t="n">
-        <v>6634350</v>
+        <v>6634416</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2091,17 +2023,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Återfynd</t>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,34 +2047,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Anders Björkén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Anders Björkén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763818</v>
+        <v>107816278</v>
       </c>
       <c r="B14" t="n">
-        <v>56856</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,53 +2076,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100065</v>
+        <v>1223</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Rikfruktig blemlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Phlyctis agelaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Flot.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norreda torp, V, Upl</t>
+          <t>Eda, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>662750</v>
+        <v>662619</v>
       </c>
       <c r="R14" t="n">
-        <v>6634176</v>
+        <v>6634022</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2215,12 +2131,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,15 +2161,3631 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>108161038</v>
+      </c>
+      <c r="B15" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>662869</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6634350</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 ex. i barrmatta och gles mossvegetation, under gran, på blockrikt, litet höjdparti. Trädskikt består huvudsakligen av gran, men enstaka klen björk i närheten samt en lindgrupp.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ca. 40-årig granplantering, på blockrikt, litet höjdparti.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122492111</v>
+      </c>
+      <c r="B16" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>662869</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6634351</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Återfynd på lokalen upptäckt av Aronsson &amp; Björkén 2023.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Ung granskog (ca 40 år).</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123763916</v>
+      </c>
+      <c r="B17" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>662867</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6634350</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Björn Bråvander</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>106088712</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83312</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1467</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rödbrun blekspik</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sclerophora coniophaea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norrsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>663058</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6634513</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Anders Björkén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>111424396</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92358</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1619</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Apelticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Aurantiporus fissilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) H.Jahn ex Ryvarden</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norrsjön, Norrsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>662973</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6634316</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-08-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 fruktkroppar på två träd ett stående dött träd och en låga.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>108161037</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>662872</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6634388</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-04-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca. 10 dm2 på naken ved på gammal, mossbevuxen eklåga, omkr. ca. 130 cm.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Mittemellan ung och medelåldrig granplantering.</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Naken ved på gammal, mossbevuxen eklåga, omkr. ca. 130 cm. # Ek</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>111611133</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93136</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rutskinn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Xylobolus frustulatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Boidin</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norredatorp, SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>662867</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6634378</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca. 0,5 m2 på naken ved på gammal eklåga, omkr. ca. 170 cm.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Mellan två granplanteringar, ca. 20 och 40 år gamla, med inslag av lövträd och hassel.</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Ek</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Naken ved på gammal eklåga, omkr. ca. 170 cm. # Ek</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7105614</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,0 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>662786</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6634319</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>107817897</v>
+      </c>
+      <c r="B23" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Eda, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>662547</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6634021</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122486174</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>662822</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6634336</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>75728186</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78728</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6436</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gulpudrad spiklav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calicium adspersum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>663055</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6634508</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2005-04-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2005-04-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På stammen av levande ek, omkr. 506 cm.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>75742487</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>663055</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6634508</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2005-04-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2005-04-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På stammen av levande ek, omkr. 506 cm.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>106088706</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6443</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sotlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Acolium inquinans</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Sm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norrsjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>663058</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6634513</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Anders Björkén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>7105633</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,3 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>663016</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6634430</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>62588795</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>662827</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6634188</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2 dm2 på levande asp, omkr. 153 cm.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>62588798</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80367</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6457</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dvärgtufs</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scytinium teretiusculum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>662877</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6634205</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På levande asp, omkr. 102 cm.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7105643</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,0 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>662761</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6634309</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Aspstammens omkrets= 86 cm</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7105644</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,0 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>662768</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6634299</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Aspstammens omkrets= 135 cm</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>62588814</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>662867</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6634196</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 dm2 på bark på asphögstubbe, omkr. 95 cm.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark på asphögstubbe. # Asp</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>62588815</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>662876</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6634188</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca. 20 dm2 på bark på asphögstubbe, omkr. 86 cm.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark på asphögstubbe. # Asp</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>62588823</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>662877</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6634205</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2 dm2 på levande asp, omkr. 102 cm.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>75749863</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>662985</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6634321</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ca. 15 dm2 på stammen av levande asp, omkr. 157 cm.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>75749864</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norredatorp 6 km SO om Funbo kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>662967</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6634321</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2006-02-03</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ca. 35 dm2 på stammen av levande ek, omkr. 187 cm.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stammen av levande ek. # Skogsek</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>62588848</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Eda 3,5 km ONO om Lagga kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>662847</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6634186</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2006-02-21</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>0,5 dm2 på levande asp, omkr. 128 cm.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123763818</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>662750</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6634176</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>16823148</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,0 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>662785</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6634298</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2014-09-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Ved # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson, Åke Lindelöw</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123763831</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57364</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>662841</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6634280</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123763945</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norreda torp, V, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>662934</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6634368</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>65879747</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106409</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>200 m V om Norredatorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>662747</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6634237</v>
+      </c>
+      <c r="S43" t="n">
+        <v>100</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>1999-01-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>1999-12-31</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mats Thulin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Upplands Flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>7105586</v>
+      </c>
+      <c r="B44" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,3 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>663016</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6634430</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>7105587</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lagga kyrka, 4,0 km NO-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>662786</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6634319</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lagga</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44867-2023 artfynd.xlsx
+++ b/artfynd/A 44867-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111611166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111424406</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111611161</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75739869</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1240,6 +1265,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65874240</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16830581</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,6 +1505,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/385227</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7105650</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588870</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1825,6 +1875,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75954920</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1954,6 +2009,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111611137</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2062,6 +2122,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107764023</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2170,6 +2235,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107816278</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2286,6 +2356,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108161038</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122492111</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2523,6 +2603,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763916</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2631,6 +2716,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106088712</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2759,6 +2849,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111424396</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2885,6 +2980,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108161037</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3011,6 +3111,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111611133</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3135,6 +3240,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7105614</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3243,6 +3353,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107817897</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3340,6 +3455,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122486174</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3452,6 +3572,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75728186</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3564,6 +3689,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75742487</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3672,6 +3802,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106088706</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3790,6 +3925,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7105633</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3911,6 +4051,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588795</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4023,6 +4168,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588798</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4154,6 +4304,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7105643</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4276,6 +4431,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7105644</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4397,6 +4557,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588814</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4518,6 +4683,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588815</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4639,6 +4809,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588823</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4760,6 +4935,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749863</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4881,6 +5061,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749864</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5002,6 +5187,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62588848</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5115,6 +5305,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763818</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5245,6 +5440,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16823148</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5372,6 +5572,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763831</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5478,6 +5683,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763945</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5584,6 +5794,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65879747</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5685,6 +5900,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7105586</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5786,8 +6006,59 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7105587</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>